--- a/.claude/project/requirements/REQ-BUPA-001-carga-portal/TestPlan-REQ-001.xlsx
+++ b/.claude/project/requirements/REQ-BUPA-001-carga-portal/TestPlan-REQ-001.xlsx
@@ -6,9 +6,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan de Pruebas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V°B Usuario" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ok Técnico" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan de Pruebas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V°B Usuario" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ok Técnico" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="B2B">#REF!</definedName>
@@ -54,6 +55,7 @@
     <definedName name="Transversales">#REF!</definedName>
     <definedName name="Usuarios">#REF!</definedName>
     <definedName name="valores_de_período_de_categorías_de_gastos_mostradas">OFFSET(categorías_de_gastos_mostradas,,período)</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Plan de Pruebas'!$B$5:$K$5</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -61,11 +63,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="44">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -336,8 +339,59 @@
       <color theme="0"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000066CC"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0000B050"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="28">
     <fill>
       <patternFill/>
     </fill>
@@ -444,6 +498,60 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.499984740745262"/>
         <bgColor rgb="FF1A1A2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000066CC"/>
+        <bgColor rgb="000066CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
+        <bgColor rgb="0000B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB3B"/>
+        <bgColor rgb="00FFEB3B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDBDBD"/>
+        <bgColor rgb="00BDBDBD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF9800"/>
+        <bgColor rgb="00FF9800"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCCCCC"/>
+        <bgColor rgb="00CCCCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -909,7 +1017,7 @@
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1237,6 +1345,54 @@
     <xf numFmtId="165" fontId="14" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1244,6 +1400,80 @@
     <cellStyle name="Percent 2" xfId="2"/>
     <cellStyle name="Excel Built-in Heading 2" xfId="3"/>
   </cellStyles>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="0000B050"/>
+          <bgColor rgb="0000B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FF0000"/>
+          <bgColor rgb="00FF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB3B"/>
+          <bgColor rgb="00FFEB3B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00BDBDBD"/>
+          <bgColor rgb="00BDBDBD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="004472C4"/>
+          <bgColor rgb="004472C4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FF9800"/>
+          <bgColor rgb="00FF9800"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1631,6 +1861,267 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="2" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="127" t="inlineStr">
+        <is>
+          <t>DASHBOARD QA - REQ-BUPA-001 - Verificacion Carga Portal Pacientes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="128" t="inlineStr">
+        <is>
+          <t>Mayo 2026  |  QA Lead: Jaime Quinelen Villar  |  Metricas en tiempo real</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="129" t="inlineStr">
+        <is>
+          <t>Metrica</t>
+        </is>
+      </c>
+      <c r="C4" s="129" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="E4" s="129" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="F4" s="129" t="inlineStr">
+        <is>
+          <t>Cant</t>
+        </is>
+      </c>
+      <c r="G4" s="129" t="inlineStr">
+        <is>
+          <t>% del Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="130" t="inlineStr">
+        <is>
+          <t>Total Casos</t>
+        </is>
+      </c>
+      <c r="C5" s="131">
+        <f>COUNTA('Plan de Pruebas'!B6:B17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="130" t="inlineStr">
+        <is>
+          <t>Exitoso</t>
+        </is>
+      </c>
+      <c r="C6" s="131">
+        <f>COUNTIF('Plan de Pruebas'!I6:I17,"Exitoso")</f>
+        <v/>
+      </c>
+      <c r="E6" s="132" t="inlineStr">
+        <is>
+          <t>Exitoso</t>
+        </is>
+      </c>
+      <c r="F6" s="133">
+        <f>COUNTIF('Plan de Pruebas'!I6:I17,"Exitoso")</f>
+        <v/>
+      </c>
+      <c r="G6" s="134">
+        <f>IF(C5=0,0,=COUNTIF('Plan de Pruebas'!I6:I17,"Exitoso")/C5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="130" t="inlineStr">
+        <is>
+          <t>Fallido</t>
+        </is>
+      </c>
+      <c r="C7" s="131">
+        <f>COUNTIF('Plan de Pruebas'!I6:I17,"Fallido")</f>
+        <v/>
+      </c>
+      <c r="E7" s="132" t="inlineStr">
+        <is>
+          <t>Fallido</t>
+        </is>
+      </c>
+      <c r="F7" s="135">
+        <f>COUNTIF('Plan de Pruebas'!I6:I17,"Fallido")</f>
+        <v/>
+      </c>
+      <c r="G7" s="134">
+        <f>IF(C5=0,0,=COUNTIF('Plan de Pruebas'!I6:I17,"Fallido")/C5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="130" t="inlineStr">
+        <is>
+          <t>En pruebas</t>
+        </is>
+      </c>
+      <c r="C8" s="131">
+        <f>COUNTIF('Plan de Pruebas'!I6:I17,"En pruebas")</f>
+        <v/>
+      </c>
+      <c r="E8" s="132" t="inlineStr">
+        <is>
+          <t>En pruebas</t>
+        </is>
+      </c>
+      <c r="F8" s="136">
+        <f>COUNTIF('Plan de Pruebas'!I6:I17,"En pruebas")</f>
+        <v/>
+      </c>
+      <c r="G8" s="134">
+        <f>IF(C5=0,0,=COUNTIF('Plan de Pruebas'!I6:I17,"En pruebas")/C5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="130" t="inlineStr">
+        <is>
+          <t>Bloqueado</t>
+        </is>
+      </c>
+      <c r="C9" s="131">
+        <f>COUNTIF('Plan de Pruebas'!I6:I17,"Bloqueado")</f>
+        <v/>
+      </c>
+      <c r="E9" s="132" t="inlineStr">
+        <is>
+          <t>Bloqueado</t>
+        </is>
+      </c>
+      <c r="F9" s="137">
+        <f>COUNTIF('Plan de Pruebas'!I6:I17,"Bloqueado")</f>
+        <v/>
+      </c>
+      <c r="G9" s="134">
+        <f>IF(C5=0,0,=COUNTIF('Plan de Pruebas'!I6:I17,"Bloqueado")/C5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="130" t="inlineStr">
+        <is>
+          <t>Por Ejecutar</t>
+        </is>
+      </c>
+      <c r="C10" s="131">
+        <f>COUNTIF('Plan de Pruebas'!I6:I17,"Por Ejecutar")</f>
+        <v/>
+      </c>
+      <c r="E10" s="132" t="inlineStr">
+        <is>
+          <t>Por Ejecutar</t>
+        </is>
+      </c>
+      <c r="F10" s="138">
+        <f>COUNTIF('Plan de Pruebas'!I6:I17,"Por Ejecutar")</f>
+        <v/>
+      </c>
+      <c r="G10" s="134">
+        <f>IF(C5=0,0,=COUNTIF('Plan de Pruebas'!I6:I17,"Por Ejecutar")/C5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="130" t="inlineStr">
+        <is>
+          <t>Ok Tecnico</t>
+        </is>
+      </c>
+      <c r="C11" s="131">
+        <f>COUNTIF('Plan de Pruebas'!I6:I17,"Ok Tecnico")</f>
+        <v/>
+      </c>
+      <c r="E11" s="132" t="inlineStr">
+        <is>
+          <t>Ok Tecnico</t>
+        </is>
+      </c>
+      <c r="F11" s="139">
+        <f>COUNTIF('Plan de Pruebas'!I6:I17,"Ok Tecnico")</f>
+        <v/>
+      </c>
+      <c r="G11" s="134">
+        <f>IF(C5=0,0,=COUNTIF('Plan de Pruebas'!I6:I17,"Ok Tecnico")/C5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="130" t="inlineStr">
+        <is>
+          <t>No Aplica</t>
+        </is>
+      </c>
+      <c r="C12" s="131">
+        <f>COUNTIF('Plan de Pruebas'!I6:I17,"No Aplica")</f>
+        <v/>
+      </c>
+      <c r="E12" s="132" t="inlineStr">
+        <is>
+          <t>No Aplica</t>
+        </is>
+      </c>
+      <c r="F12" s="140">
+        <f>COUNTIF('Plan de Pruebas'!I6:I17,"No Aplica")</f>
+        <v/>
+      </c>
+      <c r="G12" s="134">
+        <f>IF(C5=0,0,=COUNTIF('Plan de Pruebas'!I6:I17,"No Aplica")/C5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="141" t="inlineStr">
+        <is>
+          <t>% Avance (Exitoso / Total)</t>
+        </is>
+      </c>
+      <c r="D14" s="142">
+        <f>IF(C5=0,0,COUNTIF('Plan de Pruebas'!I6:I17,"Exitoso")/C5)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="FF003087"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1639,15 +2130,16 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="66.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col width="3" customWidth="1" style="1" min="1" max="1"/>
-    <col width="7" customWidth="1" style="5" min="2" max="2"/>
-    <col width="32" customWidth="1" style="5" min="3" max="3"/>
-    <col width="20" customWidth="1" style="5" min="4" max="4"/>
-    <col width="36" customWidth="1" style="5" min="5" max="5"/>
+    <col width="18" customWidth="1" style="5" min="2" max="2"/>
+    <col width="42" customWidth="1" style="5" min="3" max="3"/>
+    <col width="35" customWidth="1" style="5" min="4" max="4"/>
+    <col width="55" customWidth="1" style="5" min="5" max="5"/>
     <col width="14" customWidth="1" style="5" min="6" max="6"/>
-    <col width="18" customWidth="1" style="5" min="7" max="8"/>
-    <col width="13" customWidth="1" style="5" min="9" max="9"/>
-    <col width="16" customWidth="1" style="5" min="10" max="10"/>
-    <col width="22" customWidth="1" style="5" min="11" max="11"/>
+    <col width="22" customWidth="1" style="5" min="7" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" style="5" min="9" max="9"/>
+    <col width="20" customWidth="1" style="5" min="10" max="10"/>
+    <col width="20" customWidth="1" style="5" min="11" max="11"/>
     <col width="66.5546875" customWidth="1" style="5" min="12" max="13"/>
     <col width="66.5546875" customWidth="1" style="6" min="14" max="15"/>
     <col width="66.5546875" customWidth="1" style="1" min="16" max="16384"/>
@@ -1769,7 +2261,7 @@
       <c r="N5" s="1" t="n"/>
       <c r="O5" s="1" t="n"/>
     </row>
-    <row r="6" ht="21.75" customHeight="1">
+    <row r="6" ht="55" customHeight="1">
       <c r="A6" s="13" t="n"/>
       <c r="B6" s="14" t="inlineStr">
         <is>
@@ -1825,7 +2317,7 @@
       <c r="N6" s="1" t="n"/>
       <c r="O6" s="1" t="n"/>
     </row>
-    <row r="7" ht="21.75" customHeight="1">
+    <row r="7" ht="55" customHeight="1">
       <c r="A7" s="13" t="n"/>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -1881,7 +2373,7 @@
       <c r="N7" s="1" t="n"/>
       <c r="O7" s="1" t="n"/>
     </row>
-    <row r="8" ht="21.75" customHeight="1">
+    <row r="8" ht="55" customHeight="1">
       <c r="A8" s="13" t="n"/>
       <c r="B8" s="14" t="inlineStr">
         <is>
@@ -1937,7 +2429,7 @@
       <c r="N8" s="1" t="n"/>
       <c r="O8" s="1" t="n"/>
     </row>
-    <row r="9" ht="21.75" customHeight="1">
+    <row r="9" ht="55" customHeight="1">
       <c r="A9" s="13" t="n"/>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -1992,7 +2484,7 @@
       <c r="N9" s="1" t="n"/>
       <c r="O9" s="1" t="n"/>
     </row>
-    <row r="10" ht="21.75" customHeight="1">
+    <row r="10" ht="55" customHeight="1">
       <c r="A10" s="13" t="n"/>
       <c r="B10" s="14" t="inlineStr">
         <is>
@@ -2047,7 +2539,7 @@
       <c r="N10" s="1" t="n"/>
       <c r="O10" s="1" t="n"/>
     </row>
-    <row r="11" ht="21.75" customHeight="1">
+    <row r="11" ht="55" customHeight="1">
       <c r="A11" s="13" t="n"/>
       <c r="B11" s="19" t="inlineStr">
         <is>
@@ -2102,7 +2594,7 @@
       <c r="N11" s="1" t="n"/>
       <c r="O11" s="1" t="n"/>
     </row>
-    <row r="12" ht="21.75" customHeight="1">
+    <row r="12" ht="55" customHeight="1">
       <c r="A12" s="13" t="n"/>
       <c r="B12" s="14" t="inlineStr">
         <is>
@@ -2157,7 +2649,7 @@
       <c r="N12" s="1" t="n"/>
       <c r="O12" s="1" t="n"/>
     </row>
-    <row r="13" ht="21.75" customHeight="1">
+    <row r="13" ht="55" customHeight="1">
       <c r="A13" s="13" t="n"/>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -2212,7 +2704,7 @@
       <c r="N13" s="1" t="n"/>
       <c r="O13" s="1" t="n"/>
     </row>
-    <row r="14" ht="21.75" customHeight="1">
+    <row r="14" ht="55" customHeight="1">
       <c r="A14" s="13" t="n"/>
       <c r="B14" s="14" t="inlineStr">
         <is>
@@ -2267,7 +2759,7 @@
       <c r="N14" s="1" t="n"/>
       <c r="O14" s="1" t="n"/>
     </row>
-    <row r="15" ht="21.75" customHeight="1">
+    <row r="15" ht="55" customHeight="1">
       <c r="A15" s="13" t="n"/>
       <c r="B15" s="19" t="inlineStr">
         <is>
@@ -2322,7 +2814,7 @@
       <c r="N15" s="1" t="n"/>
       <c r="O15" s="1" t="n"/>
     </row>
-    <row r="16" ht="21.75" customHeight="1">
+    <row r="16" ht="55" customHeight="1">
       <c r="A16" s="13" t="n"/>
       <c r="B16" s="14" t="inlineStr">
         <is>
@@ -2377,7 +2869,7 @@
       <c r="N16" s="1" t="n"/>
       <c r="O16" s="1" t="n"/>
     </row>
-    <row r="17" ht="21.75" customHeight="1">
+    <row r="17" ht="55" customHeight="1">
       <c r="A17" s="13" t="n"/>
       <c r="B17" s="19" t="inlineStr">
         <is>
@@ -14093,6 +14585,7 @@
       <c r="M752" s="37" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="B5:K5"/>
   <mergeCells count="6">
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="C24:K24"/>
@@ -14101,13 +14594,38 @@
     <mergeCell ref="G2:K3"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <conditionalFormatting sqref="I6:I17">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" text="Exitoso">
+      <formula>NOT(ISERROR(SEARCH("Exitoso",I1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" text="Fallido">
+      <formula>NOT(ISERROR(SEARCH("Fallido",I1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="2" text="En pruebas">
+      <formula>NOT(ISERROR(SEARCH("En pruebas",I1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="4" operator="containsText" dxfId="3" text="Bloqueado">
+      <formula>NOT(ISERROR(SEARCH("Bloqueado",I1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="5" operator="containsText" dxfId="4" text="Ok Tecnico">
+      <formula>NOT(ISERROR(SEARCH("Ok Tecnico",I1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="6" operator="containsText" dxfId="5" text="Por Ejecutar">
+      <formula>NOT(ISERROR(SEARCH("Por Ejecutar",I1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="I6:I17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor invalido" error="Seleccione un estado de la lista." type="list">
+      <formula1>"En pruebas,Exitoso,Fallido,Bloqueado,Por Ejecutar,Ok Tecnico,No Aplica"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1D6A39"/>
@@ -14198,7 +14716,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="64" t="inlineStr">
         <is>
-          <t>Proyecto: Por definir  |  QA Lead: Jaime Quiñelen  |  Fecha: Abril 2026  |  Versión: v1.0</t>
+          <t>Proyecto: REQ-BUPA-001 - Verificacion de carga del Portal Pacientes  |  QA Lead: Jaime Quinelen Villar  |  Fecha: Mayo 2026  |  Version: v1.0</t>
         </is>
       </c>
       <c r="B8" s="109" t="n"/>
@@ -14209,6 +14727,7 @@
       <c r="G8" s="109" t="n"/>
       <c r="H8" s="110" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="15" customHeight="1"/>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="65" t="inlineStr">
@@ -14771,7 +15290,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
@@ -14860,7 +15379,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="79" t="inlineStr">
         <is>
-          <t>Proyecto: Por definir  |  QA Lead: Jaime Quiñelen  |  Fecha: Abril 2026  |  Versión: v1.0</t>
+          <t>Proyecto: REQ-BUPA-001 - Verificacion de carga del Portal Pacientes  |  QA Lead: Jaime Quinelen Villar  |  Fecha: Mayo 2026  |  Version: v1.0</t>
         </is>
       </c>
       <c r="B8" s="109" t="n"/>
@@ -14871,6 +15390,7 @@
       <c r="G8" s="109" t="n"/>
       <c r="H8" s="110" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="15" customHeight="1" thickBot="1"/>
     <row r="11" ht="22.5" customHeight="1" thickBot="1">
       <c r="A11" s="80" t="inlineStr">
@@ -15094,6 +15614,7 @@
       <c r="G23" s="114" t="n"/>
       <c r="H23" s="115" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="B25" s="54" t="inlineStr">
         <is>
@@ -15352,6 +15873,7 @@
       <c r="G51" s="114" t="n"/>
       <c r="H51" s="115" t="n"/>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="71" t="inlineStr">
         <is>
